--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488129_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488129_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7543</v>
+        <v>2.6055</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2183</v>
+        <v>-0.0225</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9727</v>
+        <v>2.6279</v>
       </c>
       <c r="G2" t="n">
         <v>2.7048</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5486</v>
+        <v>0.3998</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.092</v>
+        <v>0.1039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.2959</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3139</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1579</v>
+        <v>2.3814</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1702</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.0123</v>
+        <v>2.2925</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6268</v>
+        <v>-0.2146</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7757</v>
+        <v>-1.322</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1489</v>
+        <v>1.1074</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6641</v>
+        <v>0.22</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7564</v>
+        <v>-0.4341</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9077</v>
+        <v>0.6541</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.0373</v>
+        <v>-0.4345</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9807</v>
+        <v>-0.8878</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.0566</v>
+        <v>0.4533</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5311</v>
+        <v>-0.1452</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4326</v>
+        <v>-0.4635</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0985</v>
+        <v>0.3183</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. ÁLVAREZ RICO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7698</v>
+        <v>1.6103</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5966</v>
+        <v>1.6103</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3664</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2146</v>
+        <v>1.6103</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.322</v>
+        <v>1.6103</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1074</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.22</v>
+        <v>1.6103</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4341</v>
+        <v>1.6103</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6541</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4345</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8878</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4533</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7568</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.149</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3922</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ÁLVAREZ RICO</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6103</v>
+        <v>1.3263</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6103</v>
+        <v>4.1909</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-2.8646</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6103</v>
+        <v>0.6268</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6103</v>
+        <v>1.7757</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1.1489</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6103</v>
+        <v>4.6641</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6103</v>
+        <v>2.7564</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9077</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-4.0373</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.9807</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-3.0566</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.6995</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.4533</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2462</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.7268</v>
       </c>
       <c r="E6" t="n">
         <v>1.1597</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5806</v>
+        <v>-0.4329</v>
       </c>
       <c r="G6" t="n">
         <v>2.4178</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3939</v>
+        <v>-0.2462</v>
       </c>
       <c r="T6" t="n">
         <v>0.0174</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4114</v>
+        <v>-0.2636</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2594</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5155</v>
+        <v>0.4909</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5233</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0388</v>
+        <v>1.0142</v>
       </c>
       <c r="G7" t="n">
         <v>-2.8635</v>
@@ -1000,13 +1000,13 @@
         <v>2.594</v>
       </c>
       <c r="S7" t="n">
-        <v>0.767</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>0.0684</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6986</v>
+        <v>0.674</v>
       </c>
       <c r="V7" t="n">
         <v>0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3732</v>
+        <v>0.4219</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4805</v>
+        <v>-1.3825</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8536</v>
+        <v>1.8044</v>
       </c>
       <c r="G8" t="n">
         <v>0.0041</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1102</v>
+        <v>0.1589</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1803</v>
+        <v>-0.0824</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2905</v>
+        <v>0.2412</v>
       </c>
       <c r="V8" t="n">
         <v>0.6294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1934</v>
+        <v>-0.5605</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0173</v>
+        <v>-0.3744</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2107</v>
+        <v>-0.1861</v>
       </c>
       <c r="G9" t="n">
         <v>-0.773</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1054</v>
+        <v>-0.4725</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2699</v>
+        <v>-0.1219</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3753</v>
+        <v>-0.3507</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3051</v>
+        <v>-1.403</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0435</v>
+        <v>-3.1415</v>
       </c>
       <c r="F10" t="n">
         <v>1.7385</v>
@@ -1234,10 +1234,10 @@
         <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3793</v>
+        <v>0.2814</v>
       </c>
       <c r="T10" t="n">
-        <v>0.199</v>
+        <v>0.1011</v>
       </c>
       <c r="U10" t="n">
         <v>0.1803</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9616</v>
+        <v>-1.6432</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2437</v>
+        <v>0.0501</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7178</v>
+        <v>-1.6932</v>
       </c>
       <c r="G11" t="n">
         <v>-1.132</v>
@@ -1312,13 +1312,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1266</v>
+        <v>0.1918</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4166</v>
+        <v>-0.1228</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.3146</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0586</v>
+        <v>-2.6702</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7046</v>
+        <v>-1.3901</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.354</v>
+        <v>-1.2801</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5381</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8501</v>
+        <v>0.2385</v>
       </c>
       <c r="T12" t="n">
-        <v>0.919</v>
+        <v>0.2335</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0689</v>
+        <v>0.005</v>
       </c>
       <c r="V12" t="n">
         <v>0.6294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4525</v>
+        <v>-2.8884</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5072</v>
+        <v>-2.1154</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9454</v>
+        <v>-0.773</v>
       </c>
       <c r="G13" t="n">
         <v>-2.835</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3587</v>
+        <v>-0.7946</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6901</v>
+        <v>-0.2984</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6685</v>
+        <v>-0.4962</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.9154</v>
+        <v>-5.5242</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.3831</v>
+        <v>-4.8934</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5323</v>
+        <v>-0.6308</v>
       </c>
       <c r="G14" t="n">
         <v>-4.9022</v>
@@ -1546,13 +1546,13 @@
         <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6427</v>
+        <v>-0.2515</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8754</v>
+        <v>-0.3858</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2328</v>
+        <v>0.1343</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.126499999999998</v>
+        <v>-5.1264</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.7433</v>
+        <v>-6.7432</v>
       </c>
       <c r="F15" t="n">
-        <v>1.616899999999999</v>
+        <v>1.6168</v>
       </c>
       <c r="G15" t="n">
         <v>-10.876</v>
@@ -1624,13 +1624,13 @@
         <v>16.6758</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8021999999999998</v>
+        <v>0.8022999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4971</v>
+        <v>-0.4972</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2994</v>
+        <v>1.2993</v>
       </c>
       <c r="V15" t="n">
         <v>0.3149</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.8159</v>
+        <v>11.8239</v>
       </c>
       <c r="E16" t="n">
-        <v>9.955</v>
+        <v>9.857100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8609</v>
+        <v>1.9669</v>
       </c>
       <c r="G16" t="n">
         <v>5.4703</v>
@@ -1702,13 +1702,13 @@
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2316</v>
+        <v>-0.2235</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2773</v>
+        <v>-0.3752</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0457</v>
+        <v>0.1517</v>
       </c>
       <c r="V16" t="n">
         <v>4.9095</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0251</v>
+        <v>2.1247</v>
       </c>
       <c r="E17" t="n">
-        <v>1.429</v>
+        <v>1.2331</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5961</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.9494</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2955</v>
+        <v>-0.1959</v>
       </c>
       <c r="T17" t="n">
-        <v>0.291</v>
+        <v>0.0951</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5865</v>
+        <v>-0.291</v>
       </c>
       <c r="V17" t="n">
         <v>0.63</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2464</v>
+        <v>1.2309</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7259</v>
+        <v>0.4321</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5205</v>
+        <v>0.7988</v>
       </c>
       <c r="G19" t="n">
         <v>1.9916</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4019</v>
+        <v>0.3864</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6703</v>
+        <v>0.3765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2684</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8883</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6221</v>
+        <v>0.8635</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6221</v>
+        <v>-1.3038</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.1672</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6221</v>
+        <v>1.0295</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6221</v>
+        <v>-0.358</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6221</v>
+        <v>0.4402</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.2115</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6221</v>
+        <v>-1.7713</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.824</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.4133</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.4977</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.2235</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.7212</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8185</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1988</v>
+        <v>0.6221</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9893</v>
+        <v>0.6221</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7905</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0295</v>
+        <v>0.6221</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.358</v>
+        <v>0.6221</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4402</v>
+        <v>0.6221</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2115</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7713</v>
+        <v>0.6221</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.824</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4133</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5646</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.909</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3444</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8185</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3301</v>
+        <v>-0.0765</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3047</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9745</v>
+        <v>1.2282</v>
       </c>
       <c r="G22" t="n">
         <v>0.014</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2885</v>
+        <v>-0.0348</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2848</v>
+        <v>-0.0311</v>
       </c>
       <c r="V22" t="n">
         <v>0.315</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6748</v>
       </c>
       <c r="E23" t="n">
         <v>-0.7256</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1</v>
+        <v>0.0508</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5168</v>
@@ -2248,13 +2248,13 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8498</v>
+        <v>-0.8991</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4377</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4121</v>
+        <v>-0.4614</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8589</v>
+        <v>-1.3265</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9115</v>
+        <v>-4.8096</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0526</v>
+        <v>3.4831</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2553</v>
+        <v>1.8341</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5563</v>
+        <v>1.6452</v>
       </c>
       <c r="I24" t="n">
-        <v>0.301</v>
+        <v>0.1889</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8364</v>
+        <v>0.4002</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.4229</v>
+        <v>1.6016</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4135</v>
+        <v>-1.2014</v>
       </c>
       <c r="M24" t="n">
-        <v>0.581</v>
+        <v>1.4339</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1334</v>
+        <v>0.0436</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7144</v>
+        <v>1.3903</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5558999999999999</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1117</v>
+        <v>-5.7439</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5965</v>
+        <v>0.1713</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4077</v>
+        <v>-0.0948</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1887</v>
+        <v>0.2661</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7559</v>
+        <v>0.1886</v>
       </c>
       <c r="W24" t="n">
         <v>0.6289</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3847</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0101</v>
+        <v>-1.635</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6853</v>
+        <v>-0.3915</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3248</v>
+        <v>-1.2435</v>
       </c>
       <c r="G25" t="n">
         <v>2.0696</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4121</v>
+        <v>-0.037</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="U25" t="n">
-        <v>0.135</v>
+        <v>0.2164</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.028</v>
+        <v>-1.8954</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2992</v>
+        <v>-3.1846</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2712</v>
+        <v>1.2892</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8341</v>
+        <v>-2.2553</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6452</v>
+        <v>-2.5563</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1889</v>
+        <v>0.301</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4002</v>
+        <v>-2.8364</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6016</v>
+        <v>-2.4229</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2014</v>
+        <v>-0.4135</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4339</v>
+        <v>0.581</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0436</v>
+        <v>-0.1334</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3903</v>
+        <v>0.7144</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.5205</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.7439</v>
+        <v>-1.1117</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5303</v>
+        <v>0.5599</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5844</v>
+        <v>0.1346</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0542</v>
+        <v>0.4253</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1886</v>
+        <v>-0.7559</v>
       </c>
       <c r="W26" t="n">
         <v>0.6289</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.4403</v>
+        <v>-1.3847</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.4742</v>
+        <v>-2.5898</v>
       </c>
       <c r="E27" t="n">
         <v>-0.7882</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.686</v>
+        <v>-1.8016</v>
       </c>
       <c r="G27" t="n">
         <v>0.4821</v>
@@ -2560,13 +2560,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1554</v>
+        <v>0.0398</v>
       </c>
       <c r="T27" t="n">
         <v>-0.383</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5384</v>
+        <v>0.4228</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2589</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.3236</v>
+        <v>-3.3012</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.9111</v>
+        <v>-2.5194</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4125</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-2.0811</v>
@@ -2638,13 +2638,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2164</v>
+        <v>0.2388</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.526</v>
+        <v>-0.1343</v>
       </c>
       <c r="U28" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="V28" t="n">
         <v>-2.0147</v>
@@ -2671,19 +2671,19 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>5.126500000000001</v>
+        <v>6.4321</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.6167</v>
+        <v>-1.616799999999998</v>
       </c>
       <c r="F29" t="n">
-        <v>6.743</v>
+        <v>8.048899999999998</v>
       </c>
       <c r="G29" t="n">
         <v>10.8757</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5078000000000005</v>
+        <v>0.5078000000000009</v>
       </c>
       <c r="I29" t="n">
         <v>10.3678</v>
@@ -2716,22 +2716,22 @@
         <v>12.0436</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.8021999999999999</v>
+        <v>0.5036</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.2992</v>
+        <v>-1.2994</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4969999999999998</v>
+        <v>1.8029</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.315099999999999</v>
+        <v>-0.3150999999999995</v>
       </c>
       <c r="W29" t="n">
         <v>7.866</v>
       </c>
       <c r="X29" t="n">
-        <v>-8.180899999999999</v>
+        <v>-8.180900000000001</v>
       </c>
     </row>
   </sheetData>
